--- a/artfynd/A 18159-2026 artfynd.xlsx
+++ b/artfynd/A 18159-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114566573</v>
+        <v>114566569</v>
       </c>
       <c r="B2" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588184</v>
+        <v>588151</v>
       </c>
       <c r="R2" t="n">
-        <v>6767482</v>
+        <v>6767512</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114569342</v>
+        <v>114566573</v>
       </c>
       <c r="B3" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588192</v>
+        <v>588184</v>
       </c>
       <c r="R3" t="n">
-        <v>6767496</v>
+        <v>6767482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,22 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114566569</v>
+        <v>114569342</v>
       </c>
       <c r="B4" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588151</v>
+        <v>588192</v>
       </c>
       <c r="R4" t="n">
-        <v>6767512</v>
+        <v>6767496</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
